--- a/data/trans_orig/P1406-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1406-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de úlcera de estómago en 2012</t>
+          <t>Población con diagnóstico de úlcera de estómago en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14141</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14435</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290293</t>
+          <t>288777</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273104</t>
+          <t>273610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285171</t>
+          <t>285112</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567548</t>
+          <t>567052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>579110</t>
+          <t>578959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>18942</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>16431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31236</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485767</t>
+          <t>486585</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499403</t>
+          <t>499463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506698</t>
+          <t>507334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519779</t>
+          <t>520676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>998056</t>
+          <t>998482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1016897</t>
+          <t>1017918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>985</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8502</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322102</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332580</t>
+          <t>332544</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>340039</t>
+          <t>340041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656564</t>
+          <t>656649</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664088</t>
+          <t>664081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13421</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>368449</t>
+          <t>368971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>377390</t>
+          <t>377777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386932</t>
+          <t>386992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>749512</t>
+          <t>750012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>760526</t>
+          <t>760077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201433</t>
+          <t>199968</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210663</t>
+          <t>210549</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>213898</t>
+          <t>214335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>419286</t>
+          <t>419366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>430007</t>
+          <t>430009</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264341</t>
+          <t>264355</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272940</t>
+          <t>272939</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270926</t>
+          <t>270857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539490</t>
+          <t>539844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549899</t>
+          <t>549939</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>13097</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>13175</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>650858</t>
+          <t>649691</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660712</t>
+          <t>660720</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>681304</t>
+          <t>680678</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>691737</t>
+          <t>690870</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1336048</t>
+          <t>1336912</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1350174</t>
+          <t>1350404</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20027</t>
+          <t>18448</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>35895</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>757912</t>
+          <t>756459</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>772683</t>
+          <t>772553</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>801368</t>
+          <t>802947</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815899</t>
+          <t>815908</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1564795</t>
+          <t>1564598</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1586170</t>
+          <t>1586302</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29268</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54677</t>
+          <t>54985</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31075</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57239</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65841</t>
+          <t>67000</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>104777</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3372102</t>
+          <t>3371794</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3397511</t>
+          <t>3397097</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3496129</t>
+          <t>3496677</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3522841</t>
+          <t>3523205</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6877303</t>
+          <t>6875917</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6914853</t>
+          <t>6913694</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de úlcera de estómago en 2016</t>
+          <t>Población con diagnóstico de úlcera de estómago en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288366</t>
+          <t>289028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281355</t>
+          <t>281316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573875</t>
+          <t>573422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>19426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490555</t>
+          <t>490252</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500621</t>
+          <t>500593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510805</t>
+          <t>512265</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521085</t>
+          <t>521114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1007334</t>
+          <t>1006233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1020571</t>
+          <t>1020398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -4740,97 +4740,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1820</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5865</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1932</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5868</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6879</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5934</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316745</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318565</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,39 +4868,39 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>334377</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>330444</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>336309</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>99,43%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>334377</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>330441</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>336309</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>98,26%</t>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648940</t>
+          <t>647995</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12614</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361659</t>
+          <t>360770</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>378097</t>
+          <t>379325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386312</t>
+          <t>386314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>744633</t>
+          <t>745185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>756124</t>
+          <t>755497</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205372</t>
+          <t>205892</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211655</t>
+          <t>211721</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>421726</t>
+          <t>421715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428830</t>
+          <t>428833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11762</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258900</t>
+          <t>259064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261206</t>
+          <t>261775</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271862</t>
+          <t>271851</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>524476</t>
+          <t>524217</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>534467</t>
+          <t>534177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>15225</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,47 +6162,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>11510</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>5811</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>20480</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>11510</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>5578</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>21604</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>647004</t>
+          <t>646914</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655436</t>
+          <t>655507</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>676753</t>
+          <t>676069</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688329</t>
+          <t>688909</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,47 +6275,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1336342</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1327372</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1342041</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>99,57%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1336342</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1326248</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1342274</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>15364</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>772889</t>
+          <t>772891</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>810126</t>
+          <t>810803</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>822496</t>
+          <t>822958</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1586635</t>
+          <t>1587125</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1600866</t>
+          <t>1600435</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24787</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46915</t>
+          <t>48825</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35217</t>
+          <t>37159</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>65188</t>
+          <t>67854</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3369563</t>
+          <t>3368744</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3386189</t>
+          <t>3385855</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3497627</t>
+          <t>3495717</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3520543</t>
+          <t>3520859</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6873704</t>
+          <t>6871038</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6903675</t>
+          <t>6901733</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1406-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1406-Provincia-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288777</t>
+          <t>289672</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273610</t>
+          <t>273030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285112</t>
+          <t>285179</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567052</t>
+          <t>567258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578959</t>
+          <t>578946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11374</t>
+          <t>12185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30810</t>
+          <t>31230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>486585</t>
+          <t>486071</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499463</t>
+          <t>499415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507334</t>
+          <t>507046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520676</t>
+          <t>520563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>998482</t>
+          <t>998062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1017918</t>
+          <t>1017107</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332544</t>
+          <t>332504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>340041</t>
+          <t>340042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656649</t>
+          <t>656267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664081</t>
+          <t>664082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>368971</t>
+          <t>369270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>377777</t>
+          <t>376351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386992</t>
+          <t>386961</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>750012</t>
+          <t>750200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>760077</t>
+          <t>760737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199968</t>
+          <t>201671</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210549</t>
+          <t>210584</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>214335</t>
+          <t>214257</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>419366</t>
+          <t>418924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>430009</t>
+          <t>429958</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264355</t>
+          <t>264239</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272939</t>
+          <t>272944</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270857</t>
+          <t>269826</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539844</t>
+          <t>539435</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549939</t>
+          <t>549997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19729</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649691</t>
+          <t>650893</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660720</t>
+          <t>660708</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>680678</t>
+          <t>679218</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>690870</t>
+          <t>690832</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1336912</t>
+          <t>1335682</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1350404</t>
+          <t>1350403</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18448</t>
+          <t>18773</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35895</t>
+          <t>35689</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>756459</t>
+          <t>756209</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>772553</t>
+          <t>772578</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>802947</t>
+          <t>802622</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815908</t>
+          <t>815983</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1564598</t>
+          <t>1564804</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1586302</t>
+          <t>1586191</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29682</t>
+          <t>28429</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54985</t>
+          <t>55170</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30711</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57239</t>
+          <t>57835</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>67000</t>
+          <t>65962</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>104777</t>
+          <t>104166</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3371794</t>
+          <t>3371609</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3397097</t>
+          <t>3398350</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3496677</t>
+          <t>3496081</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3523205</t>
+          <t>3522545</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6875917</t>
+          <t>6876528</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6913694</t>
+          <t>6914732</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289028</t>
+          <t>288772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281316</t>
+          <t>281223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573422</t>
+          <t>573747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581543</t>
+          <t>581547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19426</t>
+          <t>18580</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490252</t>
+          <t>489493</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500593</t>
+          <t>500502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512265</t>
+          <t>511362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521114</t>
+          <t>521104</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1006233</t>
+          <t>1007079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1020398</t>
+          <t>1020412</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330444</t>
+          <t>329459</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>647995</t>
+          <t>648133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>360770</t>
+          <t>361124</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>379325</t>
+          <t>378337</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>745185</t>
+          <t>745591</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>755497</t>
+          <t>755503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205892</t>
+          <t>205771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211721</t>
+          <t>211694</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>421715</t>
+          <t>421635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428833</t>
+          <t>428831</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11340</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259064</t>
+          <t>258633</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261775</t>
+          <t>262888</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271851</t>
+          <t>271854</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>524217</t>
+          <t>524107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>534177</t>
+          <t>534233</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15225</t>
+          <t>15560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20480</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646914</t>
+          <t>646890</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655507</t>
+          <t>655463</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>676069</t>
+          <t>675734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688909</t>
+          <t>688537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1327372</t>
+          <t>1327429</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1342041</t>
+          <t>1341780</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>18143</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>772891</t>
+          <t>772877</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>810803</t>
+          <t>810459</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>822958</t>
+          <t>822493</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1587125</t>
+          <t>1586607</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1600435</t>
+          <t>1600344</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25606</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23683</t>
+          <t>23505</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48825</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37159</t>
+          <t>36835</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>67854</t>
+          <t>66705</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3368744</t>
+          <t>3368726</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3385855</t>
+          <t>3385615</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3495717</t>
+          <t>3496666</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3520859</t>
+          <t>3521037</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6871038</t>
+          <t>6872187</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6901733</t>
+          <t>6902057</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
